--- a/data/dividends_info_20260625.xlsx
+++ b/data/dividends_info_20260625.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>65.98999786376953</v>
+        <v>65.05999755859375</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1363843050666511</v>
+        <v>0.1383338508719509</v>
       </c>
       <c r="J2" t="n">
         <v>263</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.15000152587891</v>
+        <v>65.69999694824219</v>
       </c>
       <c r="I3" t="n">
-        <v>1.07444356654688</v>
+        <v>1.065449060144482</v>
       </c>
       <c r="J3" t="n">
         <v>242</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.340000152587891</v>
+        <v>9.359999656677246</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6423982764430194</v>
+        <v>0.6410256645383222</v>
       </c>
       <c r="J4" t="n">
         <v>172</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>65.98999786376953</v>
+        <v>65.05999755859375</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1363843050666511</v>
+        <v>0.1383338508719509</v>
       </c>
       <c r="J6" t="n">
         <v>172</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.035000085830688</v>
+        <v>2.039999961853027</v>
       </c>
       <c r="I7" t="n">
-        <v>3.783783624194224</v>
+        <v>3.774509874503002</v>
       </c>
       <c r="J7" t="n">
         <v>151</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>20.46999931335449</v>
+        <v>20.47999954223633</v>
       </c>
       <c r="I8" t="n">
-        <v>1.319003463883137</v>
+        <v>1.318359404467629</v>
       </c>
       <c r="J8" t="n">
         <v>151</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.940000057220459</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I9" t="n">
-        <v>3.367003334568775</v>
+        <v>3.389830453681454</v>
       </c>
       <c r="J9" t="n">
         <v>144</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.659999847412109</v>
+        <v>5.519999980926514</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8833922499637739</v>
+        <v>0.905797104579114</v>
       </c>
       <c r="J12" t="n">
         <v>102</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.96999979019165</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J13" t="n">
         <v>95</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>20.46999931335449</v>
+        <v>20.47999954223633</v>
       </c>
       <c r="I14" t="n">
-        <v>1.319003463883137</v>
+        <v>1.318359404467629</v>
       </c>
       <c r="J14" t="n">
         <v>88</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>65.98999786376953</v>
+        <v>65.05999755859375</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1363843050666511</v>
+        <v>0.1383338508719509</v>
       </c>
       <c r="J15" t="n">
         <v>88</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.96999979019165</v>
+        <v>4.980000019073486</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7630522059128382</v>
       </c>
       <c r="J18" t="n">
         <v>39</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.460000038146973</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="I19" t="n">
-        <v>4.578754546764538</v>
+        <v>4.520795488517063</v>
       </c>
       <c r="J19" t="n">
         <v>32</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.059999942779541</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>3.448275910667963</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>25</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.05399990081787</v>
+        <v>10.06400012969971</v>
       </c>
       <c r="I21" t="n">
-        <v>2.586035434303611</v>
+        <v>2.583465785465545</v>
       </c>
       <c r="J21" t="n">
         <v>25</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>15.35999965667725</v>
+        <v>14.84000015258789</v>
       </c>
       <c r="I22" t="n">
-        <v>3.906250087311494</v>
+        <v>4.04312664306387</v>
       </c>
       <c r="J22" t="n">
         <v>25</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.441999912261963</v>
+        <v>3.415999889373779</v>
       </c>
       <c r="I23" t="n">
-        <v>6.391632934569823</v>
+        <v>6.440281239011703</v>
       </c>
       <c r="J23" t="n">
         <v>25</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.449999809265137</v>
+        <v>6.525000095367432</v>
       </c>
       <c r="I25" t="n">
-        <v>1.550387642746198</v>
+        <v>1.532567027408892</v>
       </c>
       <c r="J25" t="n">
         <v>25</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.769999980926514</v>
+        <v>5.75</v>
       </c>
       <c r="I27" t="n">
-        <v>2.079722710514309</v>
+        <v>2.08695652173913</v>
       </c>
       <c r="J27" t="n">
         <v>18</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.839999914169312</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
-        <v>5.281690300468702</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
         <v>18</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.710000038146973</v>
+        <v>4.909999847412109</v>
       </c>
       <c r="I31" t="n">
-        <v>1.486199563334604</v>
+        <v>1.42566195876553</v>
       </c>
       <c r="J31" t="n">
         <v>11</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>35.04999923706055</v>
+        <v>34.34999847412109</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4279600663768223</v>
+        <v>0.4366812421054642</v>
       </c>
       <c r="J32" t="n">
         <v>11</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>21.81999969482422</v>
+        <v>21.68000030517578</v>
       </c>
       <c r="I34" t="n">
-        <v>1.145737871203091</v>
+        <v>1.153136515133333</v>
       </c>
       <c r="J34" t="n">
         <v>-3</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>30.29999923706055</v>
+        <v>30</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6435643726402855</v>
+        <v>0.65</v>
       </c>
       <c r="J35" t="n">
         <v>-3</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.289999961853027</v>
+        <v>5.21999979019165</v>
       </c>
       <c r="I37" t="n">
-        <v>5.482041627433514</v>
+        <v>5.555555778850955</v>
       </c>
       <c r="J37" t="n">
         <v>-3</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3.684000015258789</v>
+        <v>3.686000108718872</v>
       </c>
       <c r="I38" t="n">
-        <v>4.343105302315275</v>
+        <v>4.340748651133669</v>
       </c>
       <c r="J38" t="n">
         <v>-3</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.5</v>
+        <v>2.470000028610229</v>
       </c>
       <c r="I39" t="n">
-        <v>5.544</v>
+        <v>5.611335967392061</v>
       </c>
       <c r="J39" t="n">
         <v>-3</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>46.85499954223633</v>
+        <v>46.125</v>
       </c>
       <c r="I40" t="n">
-        <v>1.344573697908377</v>
+        <v>1.365853658536585</v>
       </c>
       <c r="J40" t="n">
         <v>-3</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6.199999809265137</v>
+        <v>6.164999961853027</v>
       </c>
       <c r="I41" t="n">
-        <v>2.258064585595426</v>
+        <v>2.270884036760317</v>
       </c>
       <c r="J41" t="n">
         <v>-3</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>28.32999992370605</v>
+        <v>28.26000022888184</v>
       </c>
       <c r="I43" t="n">
-        <v>3.000352990783931</v>
+        <v>3.007784830558128</v>
       </c>
       <c r="J43" t="n">
         <v>-3</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>65.98999786376953</v>
+        <v>65.05999755859375</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1363843050666511</v>
+        <v>0.1383338508719509</v>
       </c>
       <c r="J44" t="n">
         <v>-3</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.322000026702881</v>
+        <v>6.314000129699707</v>
       </c>
       <c r="I46" t="n">
-        <v>2.867763353910544</v>
+        <v>2.871396836804034</v>
       </c>
       <c r="J46" t="n">
         <v>-3</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.720000267028809</v>
+        <v>8.689999580383301</v>
       </c>
       <c r="I47" t="n">
-        <v>2.981651284840964</v>
+        <v>2.991944908569625</v>
       </c>
       <c r="J47" t="n">
         <v>-3</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>10.23499965667725</v>
+        <v>10.22000026702881</v>
       </c>
       <c r="I48" t="n">
-        <v>2.706399699967621</v>
+        <v>2.710371749144096</v>
       </c>
       <c r="J48" t="n">
         <v>-3</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2.973999977111816</v>
+        <v>2.946000099182129</v>
       </c>
       <c r="I50" t="n">
-        <v>3.698722288048768</v>
+        <v>3.733876316926747</v>
       </c>
       <c r="J50" t="n">
         <v>-10</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1.649999976158142</v>
+        <v>1.730000019073486</v>
       </c>
       <c r="I51" t="n">
-        <v>1.454545475563071</v>
+        <v>1.387283221699233</v>
       </c>
       <c r="J51" t="n">
         <v>-10</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.005000114440918</v>
+        <v>3.019999980926514</v>
       </c>
       <c r="I52" t="n">
-        <v>5.324459031834949</v>
+        <v>5.298013278493903</v>
       </c>
       <c r="J52" t="n">
         <v>-17</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8550000190734863</v>
+        <v>0.8600000143051147</v>
       </c>
       <c r="I53" t="n">
-        <v>2.923976542958566</v>
+        <v>2.90697669583182</v>
       </c>
       <c r="J53" t="n">
         <v>-17</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>27.54999923706055</v>
+        <v>27.39999961853027</v>
       </c>
       <c r="I54" t="n">
-        <v>4.029038224098447</v>
+        <v>4.051094946911317</v>
       </c>
       <c r="J54" t="n">
         <v>-21</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4580000042915344</v>
+        <v>0.4605000019073486</v>
       </c>
       <c r="I56" t="n">
-        <v>5.02183401407997</v>
+        <v>4.994571097662566</v>
       </c>
       <c r="J56" t="n">
         <v>-24</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>19.5</v>
+        <v>19.29999923706055</v>
       </c>
       <c r="I57" t="n">
-        <v>3.076923076923077</v>
+        <v>3.108808413048321</v>
       </c>
       <c r="J57" t="n">
         <v>-24</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.039999961853027</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I58" t="n">
-        <v>2.21238938986681</v>
+        <v>2.207505416522502</v>
       </c>
       <c r="J58" t="n">
         <v>-24</v>
@@ -4803,44 +4803,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Yakkyo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>